--- a/StructureDefinition-Referenser.xlsx
+++ b/StructureDefinition-Referenser.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Referenser.xlsx
+++ b/StructureDefinition-Referenser.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="83">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -254,10 +254,16 @@
     <t>Source attribute: R1; type could not be resolved from source model</t>
   </si>
   <si>
+    <t>Arkitektur och regelverk</t>
+  </si>
+  <si>
     <t>Referenser.R2</t>
   </si>
   <si>
     <t>Source attribute: R2; type could not be resolved from source model</t>
+  </si>
+  <si>
+    <t>Nationell Informationsstruktur 2021:1</t>
   </si>
 </sst>
 </file>
@@ -843,7 +849,7 @@
         <v>78</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -911,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -940,10 +946,10 @@
         <v>77</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -994,7 +1000,7 @@
         <v>19</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>71</v>
